--- a/summary/no/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,10 +509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A2" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -526,10 +524,10 @@
       <c r="E2" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>2301</v>
       </c>
@@ -538,10 +536,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
+      <c r="A3" t="str">
+        <v>selenium</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -555,10 +551,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7701547772354261</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>2296</v>
       </c>
@@ -567,10 +563,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A4" t="str">
+        <v>tomato</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -584,10 +578,10 @@
       <c r="E4" s="3" t="n">
         <v>0.8108009172540728</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>672</v>
       </c>
@@ -596,10 +590,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
+      <c r="A5" t="str">
+        <v>green_tea</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>2</v>
@@ -613,12 +605,12 @@
       <c r="E5" s="3" t="n">
         <v>1.109156703489818</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
       <c r="H5" s="4" t="n">
         <v>83.87</v>
       </c>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>103012</v>
       </c>
@@ -627,10 +619,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
+      <c r="A6" t="str">
+        <v>quercetin</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -644,10 +634,10 @@
       <c r="E6" s="3" t="n">
         <v>0.9002344022096688</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2" t="n">
         <v>27111</v>
       </c>
@@ -656,10 +646,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>plant_protein_intake</t>
-        </is>
+      <c r="A7" t="str">
+        <v>plant_protein_intake</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -673,10 +661,10 @@
       <c r="E7" s="3" t="n">
         <v>0.8104008904442759</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="2" t="n">
         <v>87841</v>
       </c>
@@ -685,10 +673,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A8" t="str">
+        <v>eggs</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -702,10 +688,10 @@
       <c r="E8" s="3" t="n">
         <v>0.8606264155428169</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="2" t="n">
         <v>1812</v>
       </c>
@@ -714,10 +700,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
+      <c r="A9" t="str">
+        <v>vitamin_e</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>4</v>
@@ -738,7 +722,7 @@
         <v>3.723705085890995</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>75.48999999999999</v>
+        <v>75.49</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0.4983024239643537</v>
@@ -751,10 +735,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>anti_inflammatory_diet</t>
-        </is>
+      <c r="A10" t="str">
+        <v>anti_inflammatory_diet</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -768,10 +750,10 @@
       <c r="E10" s="3" t="n">
         <v>0.8902549819435438</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="2" t="n">
         <v>71421</v>
       </c>
@@ -780,10 +762,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A11" t="str">
+        <v>tea</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>5</v>
@@ -817,10 +797,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A12" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
@@ -834,12 +812,12 @@
       <c r="E12" s="3" t="n">
         <v>1.045295896623819</v>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
       <c r="H12" s="4" t="n">
         <v>49.41</v>
       </c>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="2" t="n">
         <v>4597</v>
       </c>
@@ -848,10 +826,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
+      <c r="A13" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>27</v>
@@ -885,10 +861,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A14" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>5</v>
@@ -922,10 +896,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A15" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>5</v>
@@ -959,10 +931,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A16" t="str">
+        <v>lutein</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>5</v>
@@ -996,10 +966,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>betaine</t>
-        </is>
+      <c r="A17" t="str">
+        <v>betaine</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1013,10 +981,10 @@
       <c r="E17" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1025,10 +993,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>choline</t>
-        </is>
+      <c r="A18" t="str">
+        <v>choline</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1042,10 +1008,10 @@
       <c r="E18" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1054,10 +1020,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A19" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2</v>
@@ -1071,12 +1035,12 @@
       <c r="E19" s="3" t="n">
         <v>0.950278670532427</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
       <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="2" t="n">
         <v>4112</v>
       </c>
@@ -1085,10 +1049,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>zeaxanthin</t>
-        </is>
+      <c r="A20" t="str">
+        <v>zeaxanthin</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
@@ -1102,12 +1064,12 @@
       <c r="E20" s="3" t="n">
         <v>0.9305308958112057</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1116,10 +1078,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>vitamin_b3</t>
-        </is>
+      <c r="A21" t="str">
+        <v>vitamin_b3</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1133,10 +1093,10 @@
       <c r="E21" s="3" t="n">
         <v>1.069610736564642</v>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1145,10 +1105,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A22" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>3</v>
@@ -1182,10 +1140,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>vitamin_b6</t>
-        </is>
+      <c r="A23" t="str">
+        <v>vitamin_b6</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1199,10 +1155,10 @@
       <c r="E23" s="3" t="n">
         <v>1.129236782735652</v>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1211,10 +1167,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A24" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>3</v>
@@ -1248,10 +1202,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>vitamin_b2</t>
-        </is>
+      <c r="A25" t="str">
+        <v>vitamin_b2</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1265,10 +1217,10 @@
       <c r="E25" s="3" t="n">
         <v>1.188825666118751</v>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="5"/>
       <c r="J25" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1277,10 +1229,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A26" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1294,10 +1244,10 @@
       <c r="E26" s="3" t="n">
         <v>1.049727123434263</v>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1306,10 +1256,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A27" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1323,10 +1271,10 @@
       <c r="E27" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1335,70 +1283,72 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A28" t="str">
+        <v>calcium</v>
       </c>
       <c r="B28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1.0591852706547322</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.9035715319777113</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>1.241598919253702</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.37795762072777117</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>2.9682519310279556</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0.9149861270491104</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>494621</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>vitamin_b1</v>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C29" s="3" t="n">
         <v>1.069616314941161</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.5119644960496699</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>2.234907857172984</v>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="4" t="n">
-        <v>85.51000000000001</v>
-      </c>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="2" t="n">
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="4" t="n">
+        <v>85.51</v>
+      </c>
+      <c r="I29" s="5"/>
+      <c r="J29" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K29" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="2" t="n">
-        <v>774952</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>1478</v>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A30" t="str">
+        <v>monounsaturated_fat_mufa</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1407,15 +1357,15 @@
         <v>1.1</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="5"/>
       <c r="J30" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1424,142 +1374,140 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
+      <c r="A31" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="2" t="n">
+        <v>774952</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1.1271586532561868</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.9770670508204692</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1.300176468168491</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.6378314879402918</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.9918844610713744</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>75.14</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0.10245798863837999</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>599592</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>processed_meat_intake</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1.149239018159417</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0.9369737613162469</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1.409591575973965</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.6296319129363084</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>2.09765466731294</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>77.04</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0.009426052809354803</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1766660</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>ultra_processed_food_intake</v>
+      </c>
+      <c r="B34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>1.105391974364155</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>0.9570496576537233</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>1.276599624884141</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>0.2118725844161015</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>5.767104886911577</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>80.59</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>0.1598660025955668</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>563999</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>1503</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1.149239018159417</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>0.9369737613162469</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>1.409591575973965</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>0.6296319129363084</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>2.09765466731294</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>77.04000000000001</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0.009426052809354803</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>1766660</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>5212</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>ultra_processed_food_intake</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>1.159516828778204</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>1.049863300995226</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>1.289026327823149</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
-        <v>480347</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>3330</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="C34" s="3" t="n">
-        <v>1.198753536073191</v>
+        <v>1.1812816581299752</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.920382805616512</v>
+        <v>1.0754078661566628</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.575249959766321</v>
-      </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
+        <v>1.2975787138523882</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.6427321484843646</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2.171085356668214</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0.21970887695697142</v>
+      </c>
       <c r="J34" s="2" t="n">
-        <v>1811</v>
+        <v>1127884</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>9</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A35" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>2</v>
@@ -1573,12 +1521,12 @@
       <c r="E35" s="3" t="n">
         <v>2.844820578397655</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
       <c r="H35" s="4" t="n">
-        <v>92.65000000000001</v>
-      </c>
-      <c r="I35" s="5" t="inlineStr"/>
+        <v>92.65</v>
+      </c>
+      <c r="I35" s="5"/>
       <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1587,10 +1535,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>manganese</t>
-        </is>
+      <c r="A36" t="str">
+        <v>manganese</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1604,10 +1550,10 @@
       <c r="E36" s="3" t="n">
         <v>1.905481103347211</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="5"/>
       <c r="J36" s="2" t="n">
         <v>61321</v>
       </c>
@@ -1616,128 +1562,120 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>potassium</t>
-        </is>
+      <c r="A37" t="str">
+        <v>non_nutritive_sweetener_intake</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="3" t="n">
+        <v>1.2763443304894546</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0.9973036417217132</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1.633459241320152</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5"/>
+      <c r="J37" s="2" t="n">
+        <v>115981</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>potassium</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1.279067174104721</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>0.8702945807931509</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>1.895554083552581</v>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="2" t="n">
         <v>120852</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K38" s="2" t="n">
         <v>485</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
+    <row r="39">
+      <c r="A39" t="str">
+        <v>dietary_protein_intake</v>
+      </c>
+      <c r="B39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C39" s="3" t="n">
         <v>1.302388647984454</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.7565399032150474</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>2.242071017259514</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="n">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="4" t="n">
+        <v>66.46</v>
+      </c>
+      <c r="I39" s="5"/>
+      <c r="J39" s="2" t="n">
         <v>776349</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K39" s="2" t="n">
         <v>2168</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="3" t="n">
+    <row r="40">
+      <c r="A40" t="str">
+        <v>yogurt</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>1.307892083408092</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>1.029839375952533</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>1.664203031653749</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="2" t="n">
         <v>1812</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K40" s="2" t="n">
         <v>777</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>non_nutritive_sweetener_intake</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>1.338814310253709</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>1.029919540076821</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>1.746586675661478</v>
-      </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
-        <v>80388</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>327</v>
-      </c>
-    </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
+      <c r="A41" t="str">
+        <v>red_meat</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>6</v>
@@ -1771,10 +1709,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>docosahexaenoic_acid</t>
-        </is>
+      <c r="A42" t="str">
+        <v>docosahexaenoic_acid</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
@@ -1788,10 +1724,10 @@
       <c r="E42" s="3" t="n">
         <v>2.26250941134674</v>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="5"/>
       <c r="J42" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1800,10 +1736,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
+      <c r="A43" t="str">
+        <v>omega_3_fatty_acids</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1817,10 +1751,10 @@
       <c r="E43" s="3" t="n">
         <v>2.27241730386655</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1829,105 +1763,97 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>zinc</t>
-        </is>
+      <c r="A44" t="str">
+        <v>dairy</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C44" s="3" t="n">
+        <v>1.569724301814138</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1.0957072004937733</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2.249032221705145</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.5201448178624637</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>4.737208367915377</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>72.14</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>0.028050841105591397</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>512230</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>zinc</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>1.736651373180698</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>1.019946879904872</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>2.954816153625951</v>
       </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="2" t="n">
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="2" t="n">
         <v>63257</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K45" s="2" t="n">
         <v>229</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>oleic_acid</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="3" t="n">
+    <row r="46">
+      <c r="A46" t="str">
+        <v>oleic_acid</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>1.891151114818652</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>1.198753536073191</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="2" t="n">
         <v>2143</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K46" s="2" t="n">
         <v>323</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>2.217099921035707</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>1.236889796360678</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>3.973709335859187</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0.203362121878933</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>24.17132558630012</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>0.2259507640863558</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>19420</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>1051</v>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
+      <c r="A47" t="str">
+        <v>copper</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>2</v>
@@ -1941,12 +1867,12 @@
       <c r="E47" s="3" t="n">
         <v>13.83774495311215</v>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
       <c r="H47" s="4" t="n">
-        <v>86.43000000000001</v>
-      </c>
-      <c r="I47" s="5" t="inlineStr"/>
+        <v>86.43</v>
+      </c>
+      <c r="I47" s="5"/>
       <c r="J47" s="2" t="n">
         <v>95958</v>
       </c>

--- a/summary/no/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,8 +509,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>linoleic_acid</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -524,10 +526,10 @@
       <c r="E2" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="2" t="n">
         <v>2301</v>
       </c>
@@ -536,8 +538,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>selenium</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -551,10 +555,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7701547772354261</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="2" t="n">
         <v>2296</v>
       </c>
@@ -563,8 +567,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>tomato</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -578,10 +584,10 @@
       <c r="E4" s="3" t="n">
         <v>0.8108009172540728</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>672</v>
       </c>
@@ -590,8 +596,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>green_tea</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>green_tea</t>
+        </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>2</v>
@@ -605,12 +613,12 @@
       <c r="E5" s="3" t="n">
         <v>1.109156703489818</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="4" t="n">
         <v>83.87</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>103012</v>
       </c>
@@ -619,8 +627,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>quercetin</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>quercetin</t>
+        </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -634,10 +644,10 @@
       <c r="E6" s="3" t="n">
         <v>0.9002344022096688</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="2" t="n">
         <v>27111</v>
       </c>
@@ -646,8 +656,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>plant_protein_intake</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>plant_protein_intake</t>
+        </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -661,10 +673,10 @@
       <c r="E7" s="3" t="n">
         <v>0.8104008904442759</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="2" t="n">
         <v>87841</v>
       </c>
@@ -673,8 +685,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>eggs</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -688,10 +702,10 @@
       <c r="E8" s="3" t="n">
         <v>0.8606264155428169</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="2" t="n">
         <v>1812</v>
       </c>
@@ -700,8 +714,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>vitamin_e</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>4</v>
@@ -722,10 +738,10 @@
         <v>3.723705085890995</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>75.49</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.4983024239643537</v>
+        <v>0.498302423964353</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>127855</v>
@@ -735,8 +751,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>anti_inflammatory_diet</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>anti_inflammatory_diet</t>
+        </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -750,10 +768,10 @@
       <c r="E10" s="3" t="n">
         <v>0.8902549819435438</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="2" t="n">
         <v>71421</v>
       </c>
@@ -762,8 +780,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>tea</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>5</v>
@@ -787,7 +807,7 @@
         <v>70.23</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.3215564042344249</v>
+        <v>0.3215564042344246</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>907106</v>
@@ -797,8 +817,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>folic_acid</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
@@ -812,12 +834,12 @@
       <c r="E12" s="3" t="n">
         <v>1.045295896623819</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="4" t="n">
         <v>49.41</v>
       </c>
-      <c r="I12" s="5"/>
+      <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="2" t="n">
         <v>4597</v>
       </c>
@@ -826,8 +848,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>alcohol</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>27</v>
@@ -842,7 +866,7 @@
         <v>0.8253894033052035</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.5066166105770156</v>
+        <v>0.5066166105770157</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>1.110045220411901</v>
@@ -861,8 +885,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>beta_carotene</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>5</v>
@@ -886,7 +912,7 @@
         <v>53.56</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.9064511286620557</v>
+        <v>0.9064511286620555</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>881922</v>
@@ -896,8 +922,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>vitamin_c</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>5</v>
@@ -931,8 +959,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>lutein</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>5</v>
@@ -966,8 +996,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>betaine</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -981,10 +1013,10 @@
       <c r="E17" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="5"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="2" t="n">
         <v>77208</v>
       </c>
@@ -993,8 +1025,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>choline</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1008,10 +1042,10 @@
       <c r="E18" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1020,8 +1054,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>vitamin_d</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>2</v>
@@ -1035,12 +1071,12 @@
       <c r="E19" s="3" t="n">
         <v>0.950278670532427</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5"/>
+      <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="2" t="n">
         <v>4112</v>
       </c>
@@ -1049,8 +1085,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>zeaxanthin</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>zeaxanthin</t>
+        </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
@@ -1064,12 +1102,12 @@
       <c r="E20" s="3" t="n">
         <v>0.9305308958112057</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1078,8 +1116,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>vitamin_b3</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>vitamin_b3</t>
+        </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1093,10 +1133,10 @@
       <c r="E21" s="3" t="n">
         <v>1.069610736564642</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="5"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1105,8 +1145,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>lycopene</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>3</v>
@@ -1140,8 +1182,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>vitamin_b6</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>vitamin_b6</t>
+        </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1155,10 +1199,10 @@
       <c r="E23" s="3" t="n">
         <v>1.129236782735652</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="5"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1167,8 +1211,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>total_dietary_fiber_intake</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>3</v>
@@ -1202,8 +1248,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>vitamin_b2</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>vitamin_b2</t>
+        </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1217,10 +1265,10 @@
       <c r="E25" s="3" t="n">
         <v>1.188825666118751</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="5"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1229,8 +1277,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1244,10 +1294,10 @@
       <c r="E26" s="3" t="n">
         <v>1.049727123434263</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="5"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1256,8 +1306,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>animal_protein_intake</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1271,10 +1323,10 @@
       <c r="E27" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1283,14 +1335,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>calcium</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.0591852706547322</v>
+        <v>1.059185270654732</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.9035715319777113</v>
@@ -1299,16 +1353,16 @@
         <v>1.241598919253702</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.37795762072777117</v>
+        <v>0.3779576207356611</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2.9682519310279556</v>
+        <v>2.968251930965993</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0.9149861270491104</v>
+        <v>0.9149861270491101</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>494621</v>
@@ -1318,8 +1372,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>vitamin_b1</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>2</v>
@@ -1333,12 +1389,12 @@
       <c r="E29" s="3" t="n">
         <v>2.234907857172984</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="4" t="n">
-        <v>85.51</v>
-      </c>
-      <c r="I29" s="5"/>
+        <v>85.51000000000001</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1347,8 +1403,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>monounsaturated_fat_mufa</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1362,10 +1420,10 @@
       <c r="E30" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="5"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1374,8 +1432,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>polyunsaturated_fat_pufa</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -1389,10 +1449,10 @@
       <c r="E31" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="5"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1401,14 +1461,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1.1271586532561868</v>
+        <v>1.127158653256187</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>0.9770670508204692</v>
@@ -1417,16 +1479,16 @@
         <v>1.300176468168491</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.6378314879402918</v>
+        <v>0.6378314879357913</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.9918844610713744</v>
+        <v>1.991884461085429</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>75.14</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.10245798863837999</v>
+        <v>0.10245798863838</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>599592</v>
@@ -1436,8 +1498,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>processed_meat_intake</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>6</v>
@@ -1458,7 +1522,7 @@
         <v>2.09765466731294</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>77.04</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>0.009426052809354803</v>
@@ -1471,32 +1535,34 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>ultra_processed_food_intake</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.1812816581299752</v>
+        <v>1.181281658129975</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.0754078661566628</v>
+        <v>1.075407866156663</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.2975787138523882</v>
+        <v>1.297578713852388</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.6427321484843646</v>
+        <v>0.6427321484922891</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2.171085356668214</v>
+        <v>2.171085356641445</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.21970887695697142</v>
+        <v>0.2197088769569714</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1127884</v>
@@ -1506,8 +1572,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>vitamin_a</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
       </c>
       <c r="B35" s="2" t="n">
         <v>2</v>
@@ -1521,12 +1589,12 @@
       <c r="E35" s="3" t="n">
         <v>2.844820578397655</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>92.65</v>
-      </c>
-      <c r="I35" s="5"/>
+        <v>92.65000000000001</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1535,8 +1603,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>manganese</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>manganese</t>
+        </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1550,10 +1620,10 @@
       <c r="E36" s="3" t="n">
         <v>1.905481103347211</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="5"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
         <v>61321</v>
       </c>
@@ -1562,14 +1632,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>non_nutritive_sweetener_intake</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>non_nutritive_sweetener_intake</t>
+        </is>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1.2763443304894546</v>
+        <v>1.276344330489455</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0.9973036417217132</v>
@@ -1577,12 +1649,12 @@
       <c r="E37" s="3" t="n">
         <v>1.633459241320152</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="2" t="n">
         <v>115981</v>
       </c>
@@ -1591,8 +1663,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>potassium</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1606,10 +1680,10 @@
       <c r="E38" s="3" t="n">
         <v>1.895554083552581</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1618,8 +1692,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>dietary_protein_intake</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>2</v>
@@ -1633,12 +1709,12 @@
       <c r="E39" s="3" t="n">
         <v>2.242071017259514</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="4" t="n">
-        <v>66.46</v>
-      </c>
-      <c r="I39" s="5"/>
+        <v>66.45999999999999</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="2" t="n">
         <v>776349</v>
       </c>
@@ -1647,8 +1723,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>yogurt</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -1662,10 +1740,10 @@
       <c r="E40" s="3" t="n">
         <v>1.664203031653749</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="5"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="2" t="n">
         <v>1812</v>
       </c>
@@ -1674,8 +1752,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>red_meat</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
       </c>
       <c r="B41" s="2" t="n">
         <v>6</v>
@@ -1699,7 +1779,7 @@
         <v>81.78</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>0.01747970235970359</v>
+        <v>0.01747970235970358</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1768446</v>
@@ -1709,8 +1789,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>docosahexaenoic_acid</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
@@ -1724,10 +1806,10 @@
       <c r="E42" s="3" t="n">
         <v>2.26250941134674</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="5"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1736,8 +1818,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>omega_3_fatty_acids</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1751,10 +1835,10 @@
       <c r="E43" s="3" t="n">
         <v>2.27241730386655</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="5"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1763,8 +1847,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
-        <v>dairy</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>6</v>
@@ -1773,22 +1859,22 @@
         <v>1.569724301814138</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>1.0957072004937733</v>
+        <v>1.095707200493773</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>2.249032221705145</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.5201448178624637</v>
+        <v>0.5201448178624649</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>4.737208367915377</v>
+        <v>4.737208367915367</v>
       </c>
       <c r="H44" s="4" t="n">
         <v>72.14</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0.028050841105591397</v>
+        <v>0.02805084110559141</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>512230</v>
@@ -1798,8 +1884,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>zinc</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
@@ -1813,10 +1901,10 @@
       <c r="E45" s="3" t="n">
         <v>2.954816153625951</v>
       </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="5"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="2" t="n">
         <v>63257</v>
       </c>
@@ -1825,8 +1913,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>oleic_acid</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -1840,10 +1930,10 @@
       <c r="E46" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="5"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1852,8 +1942,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>copper</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>2</v>
@@ -1867,12 +1959,12 @@
       <c r="E47" s="3" t="n">
         <v>13.83774495311215</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="4" t="n">
-        <v>86.43</v>
-      </c>
-      <c r="I47" s="5"/>
+        <v>86.43000000000001</v>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="2" t="n">
         <v>95958</v>
       </c>

--- a/summary/no/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -450,7 +450,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData>
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
@@ -509,10 +509,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>linoleic_acid</t>
-        </is>
+      <c r="A2" t="str">
+        <v>linoleic_acid</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -526,10 +524,10 @@
       <c r="E2" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="5"/>
       <c r="J2" s="2" t="n">
         <v>2301</v>
       </c>
@@ -538,10 +536,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>selenium</t>
-        </is>
+      <c r="A3" t="str">
+        <v>selenium</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -555,10 +551,10 @@
       <c r="E3" s="3" t="n">
         <v>0.7701547772354261</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
       <c r="J3" s="2" t="n">
         <v>2296</v>
       </c>
@@ -567,10 +563,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>tomato</t>
-        </is>
+      <c r="A4" t="str">
+        <v>tomato</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -584,10 +578,10 @@
       <c r="E4" s="3" t="n">
         <v>0.8108009172540728</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="2" t="n">
         <v>672</v>
       </c>
@@ -596,10 +590,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>green_tea</t>
-        </is>
+      <c r="A5" t="str">
+        <v>green_tea</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>2</v>
@@ -613,12 +605,12 @@
       <c r="E5" s="3" t="n">
         <v>1.109156703489818</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
       <c r="H5" s="4" t="n">
         <v>83.87</v>
       </c>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2" t="n">
         <v>103012</v>
       </c>
@@ -627,10 +619,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>quercetin</t>
-        </is>
+      <c r="A6" t="str">
+        <v>quercetin</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -644,10 +634,10 @@
       <c r="E6" s="3" t="n">
         <v>0.9002344022096688</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2" t="n">
         <v>27111</v>
       </c>
@@ -656,10 +646,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>plant_protein_intake</t>
-        </is>
+      <c r="A7" t="str">
+        <v>plant_protein_intake</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -673,10 +661,10 @@
       <c r="E7" s="3" t="n">
         <v>0.8104008904442759</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="2" t="n">
         <v>87841</v>
       </c>
@@ -685,10 +673,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>eggs</t>
-        </is>
+      <c r="A8" t="str">
+        <v>eggs</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -702,10 +688,10 @@
       <c r="E8" s="3" t="n">
         <v>0.8606264155428169</v>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="2" t="n">
         <v>1812</v>
       </c>
@@ -714,10 +700,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>vitamin_e</t>
-        </is>
+      <c r="A9" t="str">
+        <v>vitamin_e</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>4</v>
@@ -738,7 +722,7 @@
         <v>3.723705085890995</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>75.48999999999999</v>
+        <v>75.49</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0.498302423964353</v>
@@ -751,10 +735,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>anti_inflammatory_diet</t>
-        </is>
+      <c r="A10" t="str">
+        <v>anti_inflammatory_diet</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -768,10 +750,10 @@
       <c r="E10" s="3" t="n">
         <v>0.8902549819435438</v>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="2" t="n">
         <v>71421</v>
       </c>
@@ -780,10 +762,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>tea</t>
-        </is>
+      <c r="A11" t="str">
+        <v>tea</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>5</v>
@@ -817,10 +797,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>folic_acid</t>
-        </is>
+      <c r="A12" t="str">
+        <v>folic_acid</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
@@ -834,12 +812,12 @@
       <c r="E12" s="3" t="n">
         <v>1.045295896623819</v>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
       <c r="H12" s="4" t="n">
         <v>49.41</v>
       </c>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="2" t="n">
         <v>4597</v>
       </c>
@@ -848,47 +826,43 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>alcohol</t>
-        </is>
+      <c r="A13" t="str">
+        <v>alcohol</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.7499115595537207</v>
+        <v>0.7484880803240668</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.6812676670885198</v>
+        <v>0.6809952145158317</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.8253894033052035</v>
+        <v>0.8226701075800033</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.5066166105770157</v>
+        <v>0.5070170678198778</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.110045220411901</v>
+        <v>1.1049616313631374</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>77.52</v>
+        <v>76.85</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.001819124570496827</v>
+        <v>0.0013200939393045895</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>14136959</v>
+        <v>14214219</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>29867</v>
+        <v>30116</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>beta_carotene</t>
-        </is>
+      <c r="A14" t="str">
+        <v>beta_carotene</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>5</v>
@@ -922,10 +896,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>vitamin_c</t>
-        </is>
+      <c r="A15" t="str">
+        <v>vitamin_c</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>5</v>
@@ -959,10 +931,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>lutein</t>
-        </is>
+      <c r="A16" t="str">
+        <v>lutein</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>5</v>
@@ -996,10 +966,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>betaine</t>
-        </is>
+      <c r="A17" t="str">
+        <v>betaine</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1013,10 +981,10 @@
       <c r="E17" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1025,10 +993,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>choline</t>
-        </is>
+      <c r="A18" t="str">
+        <v>choline</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1042,10 +1008,10 @@
       <c r="E18" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="2" t="n">
         <v>77208</v>
       </c>
@@ -1054,10 +1020,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>vitamin_d</t>
-        </is>
+      <c r="A19" t="str">
+        <v>vitamin_d</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2</v>
@@ -1071,12 +1035,12 @@
       <c r="E19" s="3" t="n">
         <v>0.950278670532427</v>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
       <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="2" t="n">
         <v>4112</v>
       </c>
@@ -1085,10 +1049,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>zeaxanthin</t>
-        </is>
+      <c r="A20" t="str">
+        <v>zeaxanthin</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
@@ -1102,12 +1064,12 @@
       <c r="E20" s="3" t="n">
         <v>0.9305308958112057</v>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="2" t="n">
         <v>781129</v>
       </c>
@@ -1116,10 +1078,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>vitamin_b3</t>
-        </is>
+      <c r="A21" t="str">
+        <v>vitamin_b3</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1133,10 +1093,10 @@
       <c r="E21" s="3" t="n">
         <v>1.069610736564642</v>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1145,10 +1105,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>lycopene</t>
-        </is>
+      <c r="A22" t="str">
+        <v>lycopene</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>3</v>
@@ -1182,10 +1140,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>vitamin_b6</t>
-        </is>
+      <c r="A23" t="str">
+        <v>vitamin_b6</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1199,10 +1155,10 @@
       <c r="E23" s="3" t="n">
         <v>1.129236782735652</v>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1211,10 +1167,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>total_dietary_fiber_intake</t>
-        </is>
+      <c r="A24" t="str">
+        <v>total_dietary_fiber_intake</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>3</v>
@@ -1248,10 +1202,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>vitamin_b2</t>
-        </is>
+      <c r="A25" t="str">
+        <v>vitamin_b2</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1265,10 +1217,10 @@
       <c r="E25" s="3" t="n">
         <v>1.188825666118751</v>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="5"/>
       <c r="J25" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1277,10 +1229,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>insoluble_dietary_fiber_intake</t>
-        </is>
+      <c r="A26" t="str">
+        <v>insoluble_dietary_fiber_intake</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1294,10 +1244,10 @@
       <c r="E26" s="3" t="n">
         <v>1.049727123434263</v>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="2" t="n">
         <v>2301</v>
       </c>
@@ -1306,10 +1256,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>animal_protein_intake</t>
-        </is>
+      <c r="A27" t="str">
+        <v>animal_protein_intake</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1323,10 +1271,10 @@
       <c r="E27" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1335,10 +1283,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
+      <c r="A28" t="str">
+        <v>calcium</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>3</v>
@@ -1372,10 +1318,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>vitamin_b1</t>
-        </is>
+      <c r="A29" t="str">
+        <v>vitamin_b1</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>2</v>
@@ -1389,12 +1333,12 @@
       <c r="E29" s="3" t="n">
         <v>2.234907857172984</v>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
       <c r="H29" s="4" t="n">
-        <v>85.51000000000001</v>
-      </c>
-      <c r="I29" s="5" t="inlineStr"/>
+        <v>85.51</v>
+      </c>
+      <c r="I29" s="5"/>
       <c r="J29" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1403,10 +1347,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>monounsaturated_fat_mufa</t>
-        </is>
+      <c r="A30" t="str">
+        <v>monounsaturated_fat_mufa</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1420,10 +1362,10 @@
       <c r="E30" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="5"/>
       <c r="J30" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1432,10 +1374,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>polyunsaturated_fat_pufa</t>
-        </is>
+      <c r="A31" t="str">
+        <v>polyunsaturated_fat_pufa</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -1449,10 +1389,10 @@
       <c r="E31" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="5"/>
       <c r="J31" s="2" t="n">
         <v>774952</v>
       </c>
@@ -1461,10 +1401,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>sugar_sweetened_beverage_intake</t>
-        </is>
+      <c r="A32" t="str">
+        <v>sugar_sweetened_beverage_intake</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>4</v>
@@ -1498,10 +1436,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>processed_meat_intake</t>
-        </is>
+      <c r="A33" t="str">
+        <v>processed_meat_intake</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>6</v>
@@ -1522,7 +1458,7 @@
         <v>2.09765466731294</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>77.04000000000001</v>
+        <v>77.04</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>0.009426052809354803</v>
@@ -1535,10 +1471,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ultra_processed_food_intake</t>
-        </is>
+      <c r="A34" t="str">
+        <v>ultra_processed_food_intake</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>3</v>
@@ -1572,10 +1506,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>vitamin_a</t>
-        </is>
+      <c r="A35" t="str">
+        <v>vitamin_a</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>2</v>
@@ -1589,12 +1521,12 @@
       <c r="E35" s="3" t="n">
         <v>2.844820578397655</v>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
       <c r="H35" s="4" t="n">
-        <v>92.65000000000001</v>
-      </c>
-      <c r="I35" s="5" t="inlineStr"/>
+        <v>92.65</v>
+      </c>
+      <c r="I35" s="5"/>
       <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
@@ -1603,10 +1535,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>manganese</t>
-        </is>
+      <c r="A36" t="str">
+        <v>manganese</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -1620,10 +1550,10 @@
       <c r="E36" s="3" t="n">
         <v>1.905481103347211</v>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="5"/>
       <c r="J36" s="2" t="n">
         <v>61321</v>
       </c>
@@ -1632,10 +1562,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>non_nutritive_sweetener_intake</t>
-        </is>
+      <c r="A37" t="str">
+        <v>non_nutritive_sweetener_intake</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
@@ -1649,12 +1577,12 @@
       <c r="E37" s="3" t="n">
         <v>1.633459241320152</v>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
       <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5" t="inlineStr"/>
+      <c r="I37" s="5"/>
       <c r="J37" s="2" t="n">
         <v>115981</v>
       </c>
@@ -1663,10 +1591,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>potassium</t>
-        </is>
+      <c r="A38" t="str">
+        <v>potassium</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -1680,10 +1606,10 @@
       <c r="E38" s="3" t="n">
         <v>1.895554083552581</v>
       </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5"/>
       <c r="J38" s="2" t="n">
         <v>120852</v>
       </c>
@@ -1692,10 +1618,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>dietary_protein_intake</t>
-        </is>
+      <c r="A39" t="str">
+        <v>dietary_protein_intake</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>2</v>
@@ -1709,12 +1633,12 @@
       <c r="E39" s="3" t="n">
         <v>2.242071017259514</v>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
       <c r="H39" s="4" t="n">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="I39" s="5" t="inlineStr"/>
+        <v>66.46</v>
+      </c>
+      <c r="I39" s="5"/>
       <c r="J39" s="2" t="n">
         <v>776349</v>
       </c>
@@ -1723,10 +1647,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>yogurt</t>
-        </is>
+      <c r="A40" t="str">
+        <v>yogurt</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -1740,10 +1662,10 @@
       <c r="E40" s="3" t="n">
         <v>1.664203031653749</v>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="5"/>
       <c r="J40" s="2" t="n">
         <v>1812</v>
       </c>
@@ -1752,10 +1674,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>red_meat</t>
-        </is>
+      <c r="A41" t="str">
+        <v>red_meat</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>6</v>
@@ -1789,10 +1709,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>docosahexaenoic_acid</t>
-        </is>
+      <c r="A42" t="str">
+        <v>docosahexaenoic_acid</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
@@ -1806,10 +1724,10 @@
       <c r="E42" s="3" t="n">
         <v>2.26250941134674</v>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="5"/>
       <c r="J42" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1818,10 +1736,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>omega_3_fatty_acids</t>
-        </is>
+      <c r="A43" t="str">
+        <v>omega_3_fatty_acids</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1</v>
@@ -1835,10 +1751,10 @@
       <c r="E43" s="3" t="n">
         <v>2.27241730386655</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="5"/>
       <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
@@ -1847,10 +1763,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>dairy</t>
-        </is>
+      <c r="A44" t="str">
+        <v>dairy</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>6</v>
@@ -1884,10 +1798,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>zinc</t>
-        </is>
+      <c r="A45" t="str">
+        <v>zinc</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1</v>
@@ -1901,10 +1813,10 @@
       <c r="E45" s="3" t="n">
         <v>2.954816153625951</v>
       </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="5"/>
       <c r="J45" s="2" t="n">
         <v>63257</v>
       </c>
@@ -1913,10 +1825,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>oleic_acid</t>
-        </is>
+      <c r="A46" t="str">
+        <v>oleic_acid</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -1930,10 +1840,10 @@
       <c r="E46" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="5"/>
       <c r="J46" s="2" t="n">
         <v>2143</v>
       </c>
@@ -1942,10 +1852,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
+      <c r="A47" t="str">
+        <v>copper</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>2</v>
@@ -1959,12 +1867,12 @@
       <c r="E47" s="3" t="n">
         <v>13.83774495311215</v>
       </c>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
       <c r="H47" s="4" t="n">
-        <v>86.43000000000001</v>
-      </c>
-      <c r="I47" s="5" t="inlineStr"/>
+        <v>86.43</v>
+      </c>
+      <c r="I47" s="5"/>
       <c r="J47" s="2" t="n">
         <v>95958</v>
       </c>

--- a/summary/no/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -450,1433 +462,1525 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
-  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>linoleic_acid</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>linoleic_acid</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.4012516644420606</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="2" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>selenium</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>selenium</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.3344926849794722</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.7701547772354261</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="2" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>2296</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>1142</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>tomato</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tomato</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.3111160697883123</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>0.8108009172540728</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="2" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>672</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>335</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>green_tea</v>
-      </c>
-      <c r="B5" s="2" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>green_tea</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>0.5124767166133164</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>0.2367619672848031</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>1.109156703489818</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4" t="n">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
         <v>83.87</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="2" t="n">
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
         <v>103012</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>536</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>quercetin</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>quercetin</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>0.6006253983961163</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.4006256157623534</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.9002344022096688</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="2" t="n">
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>27111</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>228</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>plant_protein_intake</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>plant_protein_intake</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>0.610619915389884</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>0.4506451102042392</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.8104008904442759</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="2" t="n">
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
         <v>87841</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>457</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>eggs</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>eggs</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>0.6412000957472043</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.4813011881361022</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.8606264155428169</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="2" t="n">
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="3" t="n">
         <v>1812</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>777</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>vitamin_e</v>
-      </c>
-      <c r="B9" s="2" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vitamin_e</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>0.6712591513204014</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.4539809691459988</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.9926273125874261</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>0.1210055140882807</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>3.723705085890995</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>75.49</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0.498302423964353</v>
-      </c>
-      <c r="J9" s="2" t="n">
+      <c r="F9" s="4" t="n">
+        <v>0.1210055140908499</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>3.723705085811933</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4983024239643532</v>
+      </c>
+      <c r="J9" s="3" t="n">
         <v>127855</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="K9" s="3" t="n">
         <v>2404</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>anti_inflammatory_diet</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>anti_inflammatory_diet</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>0.6805669490764156</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>0.5206505047421757</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0.8902549819435438</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="2" t="n">
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
         <v>71421</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>431</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>tea</v>
-      </c>
-      <c r="B11" s="2" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>0.7270936446838011</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>0.5572730186429885</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>0.9486645691674115</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>0.2961113832763807</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1.785359151985504</v>
-      </c>
-      <c r="H11" s="4" t="n">
+      <c r="F11" s="4" t="n">
+        <v>0.2961113832763343</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1.785359151985784</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>70.23</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I11" s="6" t="n">
         <v>0.3215564042344246</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" s="3" t="n">
         <v>907106</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K11" s="3" t="n">
         <v>3147</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>folic_acid</v>
-      </c>
-      <c r="B12" s="2" t="n">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>folic_acid</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>0.7353563995110923</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>0.5173167100803437</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>1.045295896623819</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4" t="n">
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
         <v>49.41</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="2" t="n">
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>alcohol</v>
-      </c>
-      <c r="B13" s="2" t="n">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>0.7484880803240668</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>0.6809952145158317</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>0.8226701075800033</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>0.5070170678198778</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>1.1049616313631374</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>76.85</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>0.0013200939393045895</v>
-      </c>
-      <c r="J13" s="2" t="n">
+      <c r="F13" s="4" t="n">
+        <v>0.507017067819878</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1.104961631363137</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.001320093939304585</v>
+      </c>
+      <c r="J13" s="3" t="n">
         <v>14214219</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>30116</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>beta_carotene</v>
-      </c>
-      <c r="B14" s="2" t="n">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>beta_carotene</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>0.7557081668603727</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>0.6375643919946457</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>0.8956549863849572</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>0.4498278062406948</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>1.269585440331544</v>
-      </c>
-      <c r="H14" s="4" t="n">
+      <c r="F14" s="4" t="n">
+        <v>0.4498278062406541</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1.269585440331658</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>53.56</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>0.9064511286620555</v>
-      </c>
-      <c r="J14" s="2" t="n">
+      <c r="I14" s="6" t="n">
+        <v>0.9064511286620556</v>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>881922</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>4765</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>vitamin_c</v>
-      </c>
-      <c r="B15" s="2" t="n">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>vitamin_c</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>0.7590406087904665</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>0.6146514007082959</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>0.9373486257886696</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0.4240450272610667</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>1.358682707622687</v>
-      </c>
-      <c r="H15" s="4" t="n">
+      <c r="F15" s="4" t="n">
+        <v>0.4240450272610237</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1.358682707622825</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>38.94</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0.297720986509244</v>
-      </c>
-      <c r="J15" s="2" t="n">
+      <c r="I15" s="6" t="n">
+        <v>0.2977209865092436</v>
+      </c>
+      <c r="J15" s="3" t="n">
         <v>128222</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>2559</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>lutein</v>
-      </c>
-      <c r="B16" s="2" t="n">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>lutein</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>0.7716686738745262</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>0.6812676670885198</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>0.8741528788765721</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>0.630272139746614</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0.9447863941418472</v>
-      </c>
-      <c r="H16" s="4" t="n">
+      <c r="F16" s="4" t="n">
+        <v>0.6302721397465917</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.9447863941418806</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <v>0.5550198293102779</v>
-      </c>
-      <c r="J16" s="2" t="n">
+      <c r="I16" s="6" t="n">
+        <v>0.5550198293102784</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>881922</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>4765</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>betaine</v>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="n">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>betaine</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>1.24</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="2" t="n">
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="3" t="n">
         <v>77208</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>choline</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3" t="n">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>choline</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="2" t="n">
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="3" t="n">
         <v>77208</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>vitamin_d</v>
-      </c>
-      <c r="B19" s="2" t="n">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>0.7892280209121737</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>0.6555373486867049</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>0.950278670532427</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4" t="n">
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="2" t="n">
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
         <v>4112</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="K19" s="3" t="n">
         <v>776</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>zeaxanthin</v>
-      </c>
-      <c r="B20" s="2" t="n">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>zeaxanthin</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>0.7908871412226887</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>0.672266795591652</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>0.9305308958112057</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4" t="n">
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5"/>
-      <c r="J20" s="2" t="n">
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
         <v>781129</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K20" s="3" t="n">
         <v>2616</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>vitamin_b3</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3" t="n">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>vitamin_b3</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="n">
         <v>0.8008327058475403</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>0.6012503602491741</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="4" t="n">
         <v>1.069610736564642</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="2" t="n">
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="K21" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>lycopene</v>
-      </c>
-      <c r="B22" s="2" t="n">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>lycopene</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="4" t="n">
         <v>0.84484677451711</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>0.5871352951128217</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="4" t="n">
         <v>1.215675634480141</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>0.01174800814484453</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>60.75634810699317</v>
-      </c>
-      <c r="H22" s="4" t="n">
+      <c r="F22" s="4" t="n">
+        <v>0.01174800814382701</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>60.75634811225537</v>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>78.69</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I22" s="6" t="n">
         <v>0.1356399865798741</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="3" t="n">
         <v>873444</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K22" s="3" t="n">
         <v>2860</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>vitamin_b6</v>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="3" t="n">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>vitamin_b6</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="n">
         <v>0.8506633898445702</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>0.6412000957472043</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>1.129236782735652</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="2" t="n">
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>total_dietary_fiber_intake</v>
-      </c>
-      <c r="B24" s="2" t="n">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>total_dietary_fiber_intake</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="4" t="n">
         <v>0.8684024671088</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>0.7781001776863548</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>0.9691847740261416</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>0.3170188386298179</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>2.378795052496037</v>
-      </c>
-      <c r="H24" s="4" t="n">
+      <c r="F24" s="4" t="n">
+        <v>0.3170188386233463</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>2.378795052544597</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>32.39</v>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="I24" s="6" t="n">
         <v>0.6347647391470264</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="3" t="n">
         <v>198798</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>2632</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>vitamin_b2</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="3" t="n">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>vitamin_b2</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4" t="n">
         <v>0.880549357132928</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>0.6611687215022507</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="4" t="n">
         <v>1.188825666118751</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="2" t="n">
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>insoluble_dietary_fiber_intake</v>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="3" t="n">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>insoluble_dietary_fiber_intake</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>0.920382805616512</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>0.8008327058475403</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="4" t="n">
         <v>1.049727123434263</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="2" t="n">
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="6" t="inlineStr"/>
+      <c r="J26" s="3" t="n">
         <v>2301</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>767</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>animal_protein_intake</v>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="3" t="n">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>animal_protein_intake</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>0.85</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="2" t="n">
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
         <v>774952</v>
       </c>
-      <c r="K27" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>1019</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>calcium</v>
-      </c>
-      <c r="B28" s="2" t="n">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>1.059185270654732</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>0.9035715319777113</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>1.241598919253702</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>0.3779576207356611</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>2.968251930965993</v>
-      </c>
-      <c r="H28" s="4" t="n">
+      <c r="F28" s="4" t="n">
+        <v>0.3779576207277712</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>2.968251931027956</v>
+      </c>
+      <c r="H28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="5" t="n">
-        <v>0.9149861270491101</v>
-      </c>
-      <c r="J28" s="2" t="n">
+      <c r="I28" s="6" t="n">
+        <v>0.9149861270491104</v>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>494621</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="K28" s="3" t="n">
         <v>1367</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>vitamin_b1</v>
-      </c>
-      <c r="B29" s="2" t="n">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>vitamin_b1</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>1.069616314941161</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>0.5119644960496699</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>2.234907857172984</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="4" t="n">
-        <v>85.51</v>
-      </c>
-      <c r="I29" s="5"/>
-      <c r="J29" s="2" t="n">
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="5" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="K29" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>monounsaturated_fat_mufa</v>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="3" t="n">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>monounsaturated_fat_mufa</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>1.32</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="2" t="n">
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="3" t="n">
         <v>774952</v>
       </c>
-      <c r="K30" s="2" t="n">
+      <c r="K30" s="3" t="n">
         <v>1478</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>polyunsaturated_fat_pufa</v>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="3" t="n">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>polyunsaturated_fat_pufa</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>0.93</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>1.31</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="2" t="n">
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="3" t="n">
         <v>774952</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K31" s="3" t="n">
         <v>1478</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>sugar_sweetened_beverage_intake</v>
-      </c>
-      <c r="B32" s="2" t="n">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sugar_sweetened_beverage_intake</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>1.127158653256187</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>0.9770670508204692</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>1.300176468168491</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>0.6378314879357913</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.991884461085429</v>
-      </c>
-      <c r="H32" s="4" t="n">
+      <c r="F32" s="4" t="n">
+        <v>0.6378314879402918</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1.991884461071374</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>75.14</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I32" s="6" t="n">
         <v>0.10245798863838</v>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="3" t="n">
         <v>599592</v>
       </c>
-      <c r="K32" s="2" t="n">
+      <c r="K32" s="3" t="n">
         <v>1649</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>processed_meat_intake</v>
-      </c>
-      <c r="B33" s="2" t="n">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>processed_meat_intake</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>1.149239018159417</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>0.9369737613162469</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>1.409591575973965</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>0.6296319129363084</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>2.09765466731294</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>77.04</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0.009426052809354803</v>
-      </c>
-      <c r="J33" s="2" t="n">
+      <c r="F33" s="4" t="n">
+        <v>0.6296319129363077</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>2.097654667312942</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.009426052809354796</v>
+      </c>
+      <c r="J33" s="3" t="n">
         <v>1766660</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="K33" s="3" t="n">
         <v>5212</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>ultra_processed_food_intake</v>
-      </c>
-      <c r="B34" s="2" t="n">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ultra_processed_food_intake</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>1.181281658129975</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>1.075407866156663</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>1.297578713852388</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>0.6427321484922891</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>2.171085356641445</v>
-      </c>
-      <c r="H34" s="4" t="n">
+      <c r="F34" s="4" t="n">
+        <v>0.6427321484843646</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>2.171085356668214</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="I34" s="6" t="n">
         <v>0.2197088769569714</v>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="J34" s="3" t="n">
         <v>1127884</v>
       </c>
-      <c r="K34" s="2" t="n">
+      <c r="K34" s="3" t="n">
         <v>4245</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>vitamin_a</v>
-      </c>
-      <c r="B35" s="2" t="n">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>vitamin_a</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="4" t="n">
         <v>1.225562595253664</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>0.5280311504245172</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>2.844820578397655</v>
       </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4" t="n">
-        <v>92.65</v>
-      </c>
-      <c r="I35" s="5"/>
-      <c r="J35" s="2" t="n">
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="5" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="3" t="n">
         <v>4597</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="K35" s="3" t="n">
         <v>1909</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>manganese</v>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="3" t="n">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>manganese</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="4" t="n">
         <v>1.259147309219077</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>0.8303675352604869</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>1.905481103347211</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="2" t="n">
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="3" t="n">
         <v>61321</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K36" s="3" t="n">
         <v>229</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>non_nutritive_sweetener_intake</v>
-      </c>
-      <c r="B37" s="2" t="n">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>non_nutritive_sweetener_intake</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>1.276344330489455</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>0.9973036417217132</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="4" t="n">
         <v>1.633459241320152</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="4" t="n">
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="5"/>
-      <c r="J37" s="2" t="n">
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="3" t="n">
         <v>115981</v>
       </c>
-      <c r="K37" s="2" t="n">
+      <c r="K37" s="3" t="n">
         <v>473</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>potassium</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="3" t="n">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="n">
         <v>1.279067174104721</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>0.8702945807931509</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>1.895554083552581</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="2" t="n">
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
         <v>120852</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K38" s="3" t="n">
         <v>485</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
-        <v>dietary_protein_intake</v>
-      </c>
-      <c r="B39" s="2" t="n">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dietary_protein_intake</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="4" t="n">
         <v>1.302388647984454</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>0.7565399032150474</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>2.242071017259514</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="4" t="n">
-        <v>66.46</v>
-      </c>
-      <c r="I39" s="5"/>
-      <c r="J39" s="2" t="n">
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="n">
+        <v>66.45999999999999</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="3" t="n">
         <v>776349</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K39" s="3" t="n">
         <v>2168</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
-        <v>yogurt</v>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3" t="n">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>yogurt</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4" t="n">
         <v>1.307892083408092</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>1.029839375952533</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="4" t="n">
         <v>1.664203031653749</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="2" t="n">
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="3" t="n">
         <v>1812</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="K40" s="3" t="n">
         <v>777</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
-        <v>red_meat</v>
-      </c>
-      <c r="B41" s="2" t="n">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>red_meat</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="4" t="n">
         <v>1.431037921180599</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>1.128286375676676</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="4" t="n">
         <v>1.815207887998699</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>0.6713010778247132</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>3.050597711674792</v>
-      </c>
-      <c r="H41" s="4" t="n">
+      <c r="F41" s="4" t="n">
+        <v>0.6713010778247123</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>3.050597711674797</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>81.78</v>
       </c>
-      <c r="I41" s="5" t="n">
-        <v>0.01747970235970358</v>
-      </c>
-      <c r="J41" s="2" t="n">
+      <c r="I41" s="6" t="n">
+        <v>0.0174797023597036</v>
+      </c>
+      <c r="J41" s="3" t="n">
         <v>1768446</v>
       </c>
-      <c r="K41" s="2" t="n">
+      <c r="K41" s="3" t="n">
         <v>5800</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
-        <v>docosahexaenoic_acid</v>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="3" t="n">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="4" t="n">
         <v>1.557727341926417</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>1.069804982860268</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="4" t="n">
         <v>2.26250941134674</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="2" t="n">
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="3" t="n">
         <v>84063</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="K42" s="3" t="n">
         <v>262</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
-        <v>omega_3_fatty_acids</v>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="3" t="n">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4" t="n">
         <v>1.557727341926417</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="4" t="n">
         <v>1.069804982860268</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="4" t="n">
         <v>2.27241730386655</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="2" t="n">
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="3" t="n">
         <v>84063</v>
       </c>
-      <c r="K43" s="2" t="n">
+      <c r="K43" s="3" t="n">
         <v>262</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
-        <v>dairy</v>
-      </c>
-      <c r="B44" s="2" t="n">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="4" t="n">
         <v>1.569724301814138</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>1.095707200493773</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="4" t="n">
         <v>2.249032221705145</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>0.5201448178624649</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>4.737208367915367</v>
-      </c>
-      <c r="H44" s="4" t="n">
+      <c r="F44" s="4" t="n">
+        <v>0.5201448178624637</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>4.737208367915377</v>
+      </c>
+      <c r="H44" s="5" t="n">
         <v>72.14</v>
       </c>
-      <c r="I44" s="5" t="n">
-        <v>0.02805084110559141</v>
-      </c>
-      <c r="J44" s="2" t="n">
+      <c r="I44" s="6" t="n">
+        <v>0.0280508411055914</v>
+      </c>
+      <c r="J44" s="3" t="n">
         <v>512230</v>
       </c>
-      <c r="K44" s="2" t="n">
+      <c r="K44" s="3" t="n">
         <v>2409</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
-        <v>zinc</v>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="3" t="n">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4" t="n">
         <v>1.736651373180698</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="4" t="n">
         <v>1.019946879904872</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="4" t="n">
         <v>2.954816153625951</v>
       </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="2" t="n">
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="3" t="n">
         <v>63257</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="K45" s="3" t="n">
         <v>229</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
-        <v>oleic_acid</v>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="3" t="n">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="4" t="n">
         <v>1.891151114818652</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="4" t="n">
         <v>1.198753536073191</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="4" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="2" t="n">
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="3" t="n">
         <v>2143</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="K46" s="3" t="n">
         <v>323</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
-        <v>copper</v>
-      </c>
-      <c r="B47" s="2" t="n">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>copper</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="4" t="n">
         <v>2.441469226259395</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="4" t="n">
         <v>0.4308048825855873</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="4" t="n">
         <v>13.83774495311215</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="4" t="n">
-        <v>86.43</v>
-      </c>
-      <c r="I47" s="5"/>
-      <c r="J47" s="2" t="n">
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="5" t="n">
+        <v>86.43000000000001</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="3" t="n">
         <v>95958</v>
       </c>
-      <c r="K47" s="2" t="n">
+      <c r="K47" s="3" t="n">
         <v>353</v>
       </c>
     </row>

--- a/summary/no/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_kidney_and_renal_pelvis_cancer_dietary.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,26 +514,26 @@
           <t>linoleic_acid</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.4012516644420606</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.7010934955249702</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -555,26 +543,26 @@
           <t>selenium</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.3344926849794722</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.7701547772354261</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>2296</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>1142</v>
       </c>
     </row>
@@ -584,26 +572,26 @@
           <t>tomato</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.5013031375059467</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.3111160697883123</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>0.8108009172540728</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>672</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>335</v>
       </c>
     </row>
@@ -613,28 +601,28 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>0.5124767166133164</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.2367619672848031</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="3" t="n">
         <v>1.109156703489818</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="5" t="n">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
         <v>83.87</v>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="3" t="n">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>103012</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>536</v>
       </c>
     </row>
@@ -644,26 +632,26 @@
           <t>quercetin</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0.6006253983961163</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.4006256157623534</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="3" t="n">
         <v>0.9002344022096688</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="3" t="n">
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
         <v>27111</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>228</v>
       </c>
     </row>
@@ -673,26 +661,26 @@
           <t>plant_protein_intake</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0.610619915389884</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.4506451102042392</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.8104008904442759</v>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="3" t="n">
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
         <v>87841</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>457</v>
       </c>
     </row>
@@ -702,26 +690,26 @@
           <t>eggs</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>0.6412000957472043</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.4813011881361022</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="3" t="n">
         <v>0.8606264155428169</v>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="3" t="n">
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
         <v>1812</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>777</v>
       </c>
     </row>
@@ -731,34 +719,34 @@
           <t>vitamin_e</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="3" t="n">
         <v>0.6712591513204014</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="3" t="n">
         <v>0.4539809691459988</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="3" t="n">
         <v>0.9926273125874261</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>0.1210055140908499</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>3.723705085811933</v>
-      </c>
-      <c r="H9" s="5" t="n">
+      <c r="F9" s="3" t="n">
+        <v>0.1210055140882807</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>3.723705085890995</v>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>75.48999999999999</v>
       </c>
-      <c r="I9" s="6" t="n">
-        <v>0.4983024239643532</v>
-      </c>
-      <c r="J9" s="3" t="n">
+      <c r="I9" s="5" t="n">
+        <v>0.4983024239643531</v>
+      </c>
+      <c r="J9" s="2" t="n">
         <v>127855</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>2404</v>
       </c>
     </row>
@@ -768,26 +756,26 @@
           <t>anti_inflammatory_diet</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="B10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>0.6805669490764156</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.5206505047421757</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="3" t="n">
         <v>0.8902549819435438</v>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="3" t="n">
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
         <v>71421</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>431</v>
       </c>
     </row>
@@ -797,34 +785,34 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="3" t="n">
         <v>0.7270936446838011</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="3" t="n">
         <v>0.5572730186429885</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="3" t="n">
         <v>0.9486645691674115</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>0.2961113832763343</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1.785359151985784</v>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="F11" s="3" t="n">
+        <v>0.2961113832763807</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1.785359151985504</v>
+      </c>
+      <c r="H11" s="4" t="n">
         <v>70.23</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="5" t="n">
         <v>0.3215564042344246</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" s="2" t="n">
         <v>907106</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="2" t="n">
         <v>3147</v>
       </c>
     </row>
@@ -834,28 +822,28 @@
           <t>folic_acid</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="3" t="n">
         <v>0.7353563995110923</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="3" t="n">
         <v>0.5173167100803437</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="3" t="n">
         <v>1.045295896623819</v>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="5" t="n">
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
         <v>49.41</v>
       </c>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -865,34 +853,34 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="3" t="n">
         <v>0.7484880803240668</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="3" t="n">
         <v>0.6809952145158317</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="3" t="n">
         <v>0.8226701075800033</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>0.507017067819878</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1.104961631363137</v>
-      </c>
-      <c r="H13" s="5" t="n">
+      <c r="F13" s="3" t="n">
+        <v>0.5070170678198777</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1.104961631363138</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>76.84999999999999</v>
       </c>
-      <c r="I13" s="6" t="n">
-        <v>0.001320093939304585</v>
-      </c>
-      <c r="J13" s="3" t="n">
+      <c r="I13" s="5" t="n">
+        <v>0.001320093939304584</v>
+      </c>
+      <c r="J13" s="2" t="n">
         <v>14214219</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="2" t="n">
         <v>30116</v>
       </c>
     </row>
@@ -902,34 +890,34 @@
           <t>beta_carotene</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="3" t="n">
         <v>0.7557081668603727</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.6375643919946457</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="3" t="n">
         <v>0.8956549863849572</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>0.4498278062406541</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1.269585440331658</v>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="F14" s="3" t="n">
+        <v>0.4498278062406948</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>1.269585440331544</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>53.56</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>0.9064511286620556</v>
-      </c>
-      <c r="J14" s="3" t="n">
+      <c r="I14" s="5" t="n">
+        <v>0.9064511286620555</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <v>881922</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="2" t="n">
         <v>4765</v>
       </c>
     </row>
@@ -939,34 +927,34 @@
           <t>vitamin_c</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="3" t="n">
         <v>0.7590406087904665</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="3" t="n">
         <v>0.6146514007082959</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="3" t="n">
         <v>0.9373486257886696</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>0.4240450272610237</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1.358682707622825</v>
-      </c>
-      <c r="H15" s="5" t="n">
+      <c r="F15" s="3" t="n">
+        <v>0.4240450272610667</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1.358682707622687</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>38.94</v>
       </c>
-      <c r="I15" s="6" t="n">
-        <v>0.2977209865092436</v>
-      </c>
-      <c r="J15" s="3" t="n">
+      <c r="I15" s="5" t="n">
+        <v>0.297720986509244</v>
+      </c>
+      <c r="J15" s="2" t="n">
         <v>128222</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="2" t="n">
         <v>2559</v>
       </c>
     </row>
@@ -976,34 +964,34 @@
           <t>lutein</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="3" t="n">
         <v>0.7716686738745262</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.6812676670885198</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="3" t="n">
         <v>0.8741528788765721</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0.6302721397465917</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>0.9447863941418806</v>
-      </c>
-      <c r="H16" s="5" t="n">
+      <c r="F16" s="3" t="n">
+        <v>0.630272139746614</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.9447863941418472</v>
+      </c>
+      <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <v>0.5550198293102784</v>
-      </c>
-      <c r="J16" s="3" t="n">
+      <c r="I16" s="5" t="n">
+        <v>0.5550198293102783</v>
+      </c>
+      <c r="J16" s="2" t="n">
         <v>881922</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>4765</v>
       </c>
     </row>
@@ -1013,26 +1001,26 @@
           <t>betaine</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="n">
+      <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="3" t="n">
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
         <v>77208</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -1042,26 +1030,26 @@
           <t>choline</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="n">
+      <c r="B18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="3" t="n">
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
         <v>77208</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="2" t="n">
         <v>225</v>
       </c>
     </row>
@@ -1071,28 +1059,28 @@
           <t>vitamin_d</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="3" t="n">
         <v>0.7892280209121737</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="3" t="n">
         <v>0.6555373486867049</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="3" t="n">
         <v>0.950278670532427</v>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="5" t="n">
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="3" t="n">
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
         <v>4112</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="2" t="n">
         <v>776</v>
       </c>
     </row>
@@ -1102,28 +1090,28 @@
           <t>zeaxanthin</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="3" t="n">
         <v>0.7908871412226887</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.672266795591652</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.9305308958112057</v>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="5" t="n">
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="3" t="n">
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
         <v>781129</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="2" t="n">
         <v>2616</v>
       </c>
     </row>
@@ -1133,26 +1121,26 @@
           <t>vitamin_b3</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="n">
+      <c r="B21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.8008327058475403</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.6012503602491741</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="3" t="n">
         <v>1.069610736564642</v>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="3" t="n">
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1162,34 +1150,34 @@
           <t>lycopene</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="3" t="n">
         <v>0.84484677451711</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.5871352951128217</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="3" t="n">
         <v>1.215675634480141</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>0.01174800814382701</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>60.75634811225537</v>
-      </c>
-      <c r="H22" s="5" t="n">
+      <c r="F22" s="3" t="n">
+        <v>0.01174800814484453</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>60.75634810699317</v>
+      </c>
+      <c r="H22" s="4" t="n">
         <v>78.69</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="5" t="n">
         <v>0.1356399865798741</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="J22" s="2" t="n">
         <v>873444</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="2" t="n">
         <v>2860</v>
       </c>
     </row>
@@ -1199,26 +1187,26 @@
           <t>vitamin_b6</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="n">
+      <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>0.8506633898445702</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.6412000957472043</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="3" t="n">
         <v>1.129236782735652</v>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="3" t="n">
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1228,34 +1216,34 @@
           <t>total_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="3" t="n">
         <v>0.8684024671088</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.7781001776863548</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="3" t="n">
         <v>0.9691847740261416</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>0.3170188386233463</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>2.378795052544597</v>
-      </c>
-      <c r="H24" s="5" t="n">
+      <c r="F24" s="3" t="n">
+        <v>0.3170188386298179</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>2.378795052496037</v>
+      </c>
+      <c r="H24" s="4" t="n">
         <v>32.39</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="5" t="n">
         <v>0.6347647391470264</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="J24" s="2" t="n">
         <v>198798</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="K24" s="2" t="n">
         <v>2632</v>
       </c>
     </row>
@@ -1265,26 +1253,26 @@
           <t>vitamin_b2</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="4" t="n">
+      <c r="B25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>0.880549357132928</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="3" t="n">
         <v>0.6611687215022507</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="3" t="n">
         <v>1.188825666118751</v>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="3" t="n">
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1294,26 +1282,26 @@
           <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="n">
+      <c r="B26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>0.920382805616512</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="3" t="n">
         <v>0.8008327058475403</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="3" t="n">
         <v>1.049727123434263</v>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="3" t="n">
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
         <v>2301</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="2" t="n">
         <v>767</v>
       </c>
     </row>
@@ -1323,26 +1311,26 @@
           <t>animal_protein_intake</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="n">
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
         <v>774952</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="2" t="n">
         <v>1019</v>
       </c>
     </row>
@@ -1352,34 +1340,34 @@
           <t>calcium</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="3" t="n">
         <v>1.059185270654732</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="3" t="n">
         <v>0.9035715319777113</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="3" t="n">
         <v>1.241598919253702</v>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>0.3779576207277712</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>2.968251931027956</v>
-      </c>
-      <c r="H28" s="5" t="n">
+      <c r="F28" s="3" t="n">
+        <v>0.3779576207356611</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>2.968251930965993</v>
+      </c>
+      <c r="H28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="6" t="n">
-        <v>0.9149861270491104</v>
-      </c>
-      <c r="J28" s="3" t="n">
+      <c r="I28" s="5" t="n">
+        <v>0.9149861270491101</v>
+      </c>
+      <c r="J28" s="2" t="n">
         <v>494621</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="2" t="n">
         <v>1367</v>
       </c>
     </row>
@@ -1389,28 +1377,28 @@
           <t>vitamin_b1</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="3" t="n">
         <v>1.069616314941161</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="3" t="n">
         <v>0.5119644960496699</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="3" t="n">
         <v>2.234907857172984</v>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="5" t="n">
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="4" t="n">
         <v>85.51000000000001</v>
       </c>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="3" t="n">
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -1420,26 +1408,26 @@
           <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4" t="n">
+      <c r="B30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="3" t="n">
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="2" t="n">
         <v>774952</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="2" t="n">
         <v>1478</v>
       </c>
     </row>
@@ -1449,26 +1437,26 @@
           <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="4" t="n">
+      <c r="B31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="3" t="n">
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="2" t="n">
         <v>774952</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="2" t="n">
         <v>1478</v>
       </c>
     </row>
@@ -1478,34 +1466,34 @@
           <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="3" t="n">
         <v>1.127158653256187</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="3" t="n">
         <v>0.9770670508204692</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="3" t="n">
         <v>1.300176468168491</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>0.6378314879402918</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1.991884461071374</v>
-      </c>
-      <c r="H32" s="5" t="n">
+      <c r="F32" s="3" t="n">
+        <v>0.6378314879357913</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.991884461085429</v>
+      </c>
+      <c r="H32" s="4" t="n">
         <v>75.14</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="5" t="n">
         <v>0.10245798863838</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="J32" s="2" t="n">
         <v>599592</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="2" t="n">
         <v>1649</v>
       </c>
     </row>
@@ -1515,34 +1503,34 @@
           <t>processed_meat_intake</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="3" t="n">
         <v>1.149239018159417</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="3" t="n">
         <v>0.9369737613162469</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="3" t="n">
         <v>1.409591575973965</v>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>0.6296319129363077</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>2.097654667312942</v>
-      </c>
-      <c r="H33" s="5" t="n">
+      <c r="F33" s="3" t="n">
+        <v>0.6296319129363084</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>2.09765466731294</v>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>77.04000000000001</v>
       </c>
-      <c r="I33" s="6" t="n">
-        <v>0.009426052809354796</v>
-      </c>
-      <c r="J33" s="3" t="n">
+      <c r="I33" s="5" t="n">
+        <v>0.009426052809354803</v>
+      </c>
+      <c r="J33" s="2" t="n">
         <v>1766660</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="2" t="n">
         <v>5212</v>
       </c>
     </row>
@@ -1552,34 +1540,34 @@
           <t>ultra_processed_food_intake</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="3" t="n">
         <v>1.181281658129975</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="3" t="n">
         <v>1.075407866156663</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="3" t="n">
         <v>1.297578713852388</v>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>0.6427321484843646</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>2.171085356668214</v>
-      </c>
-      <c r="H34" s="5" t="n">
+      <c r="F34" s="3" t="n">
+        <v>0.6427321484922891</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2.171085356641445</v>
+      </c>
+      <c r="H34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="5" t="n">
         <v>0.2197088769569714</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="J34" s="2" t="n">
         <v>1127884</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="2" t="n">
         <v>4245</v>
       </c>
     </row>
@@ -1589,28 +1577,28 @@
           <t>vitamin_a</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="3" t="n">
         <v>1.225562595253664</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="3" t="n">
         <v>0.5280311504245172</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="3" t="n">
         <v>2.844820578397655</v>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="5" t="n">
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
         <v>92.65000000000001</v>
       </c>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="3" t="n">
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
         <v>4597</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="2" t="n">
         <v>1909</v>
       </c>
     </row>
@@ -1620,26 +1608,26 @@
           <t>manganese</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="4" t="n">
+      <c r="B36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>1.259147309219077</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="3" t="n">
         <v>0.8303675352604869</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="3" t="n">
         <v>1.905481103347211</v>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="3" t="n">
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
         <v>61321</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="2" t="n">
         <v>229</v>
       </c>
     </row>
@@ -1649,28 +1637,28 @@
           <t>non_nutritive_sweetener_intake</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="3" t="n">
         <v>1.276344330489455</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.9973036417217132</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="3" t="n">
         <v>1.633459241320152</v>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="5" t="n">
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="6" t="inlineStr"/>
-      <c r="J37" s="3" t="n">
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
         <v>115981</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="2" t="n">
         <v>473</v>
       </c>
     </row>
@@ -1680,26 +1668,26 @@
           <t>potassium</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4" t="n">
+      <c r="B38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1.279067174104721</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="3" t="n">
         <v>0.8702945807931509</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="3" t="n">
         <v>1.895554083552581</v>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="3" t="n">
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
         <v>120852</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="K38" s="2" t="n">
         <v>485</v>
       </c>
     </row>
@@ -1709,28 +1697,28 @@
           <t>dietary_protein_intake</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="B39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="3" t="n">
         <v>1.302388647984454</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.7565399032150474</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="3" t="n">
         <v>2.242071017259514</v>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="5" t="n">
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="n">
         <v>66.45999999999999</v>
       </c>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="3" t="n">
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
         <v>776349</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="2" t="n">
         <v>2168</v>
       </c>
     </row>
@@ -1740,26 +1728,26 @@
           <t>yogurt</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="n">
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>1.307892083408092</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="3" t="n">
         <v>1.029839375952533</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="3" t="n">
         <v>1.664203031653749</v>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="3" t="n">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
         <v>1812</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="2" t="n">
         <v>777</v>
       </c>
     </row>
@@ -1769,34 +1757,34 @@
           <t>red_meat</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n">
+      <c r="B41" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="3" t="n">
         <v>1.431037921180599</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="3" t="n">
         <v>1.128286375676676</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="3" t="n">
         <v>1.815207887998699</v>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>0.6713010778247123</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>3.050597711674797</v>
-      </c>
-      <c r="H41" s="5" t="n">
+      <c r="F41" s="3" t="n">
+        <v>0.6713010778247132</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>3.050597711674792</v>
+      </c>
+      <c r="H41" s="4" t="n">
         <v>81.78</v>
       </c>
-      <c r="I41" s="6" t="n">
-        <v>0.0174797023597036</v>
-      </c>
-      <c r="J41" s="3" t="n">
+      <c r="I41" s="5" t="n">
+        <v>0.01747970235970358</v>
+      </c>
+      <c r="J41" s="2" t="n">
         <v>1768446</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="2" t="n">
         <v>5800</v>
       </c>
     </row>
@@ -1806,26 +1794,26 @@
           <t>docosahexaenoic_acid</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="4" t="n">
+      <c r="B42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>1.557727341926417</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="3" t="n">
         <v>1.069804982860268</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="3" t="n">
         <v>2.26250941134674</v>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr"/>
-      <c r="J42" s="3" t="n">
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
         <v>84063</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="2" t="n">
         <v>262</v>
       </c>
     </row>
@@ -1835,26 +1823,26 @@
           <t>omega_3_fatty_acids</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="4" t="n">
+      <c r="B43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>1.557727341926417</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="3" t="n">
         <v>1.069804982860268</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="3" t="n">
         <v>2.27241730386655</v>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="3" t="n">
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
         <v>84063</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="2" t="n">
         <v>262</v>
       </c>
     </row>
@@ -1864,34 +1852,34 @@
           <t>dairy</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="3" t="n">
         <v>1.569724301814138</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="3" t="n">
         <v>1.095707200493773</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="3" t="n">
         <v>2.249032221705145</v>
       </c>
-      <c r="F44" s="4" t="n">
-        <v>0.5201448178624637</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>4.737208367915377</v>
-      </c>
-      <c r="H44" s="5" t="n">
+      <c r="F44" s="3" t="n">
+        <v>0.5201448178624649</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>4.737208367915367</v>
+      </c>
+      <c r="H44" s="4" t="n">
         <v>72.14</v>
       </c>
-      <c r="I44" s="6" t="n">
-        <v>0.0280508411055914</v>
-      </c>
-      <c r="J44" s="3" t="n">
+      <c r="I44" s="5" t="n">
+        <v>0.02805084110559141</v>
+      </c>
+      <c r="J44" s="2" t="n">
         <v>512230</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="2" t="n">
         <v>2409</v>
       </c>
     </row>
@@ -1901,26 +1889,26 @@
           <t>zinc</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4" t="n">
+      <c r="B45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>1.736651373180698</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="3" t="n">
         <v>1.019946879904872</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="3" t="n">
         <v>2.954816153625951</v>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="3" t="n">
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="2" t="n">
         <v>63257</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="2" t="n">
         <v>229</v>
       </c>
     </row>
@@ -1930,26 +1918,26 @@
           <t>oleic_acid</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="4" t="n">
+      <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>1.891151114818652</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="3" t="n">
         <v>1.198753536073191</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="3" t="n">
         <v>2.871633714999859</v>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="3" t="n">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="2" t="n">
         <v>2143</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="2" t="n">
         <v>323</v>
       </c>
     </row>
@@ -1959,28 +1947,28 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="3" t="n">
         <v>2.441469226259395</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.4308048825855873</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="3" t="n">
         <v>13.83774495311215</v>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="5" t="n">
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="4" t="n">
         <v>86.43000000000001</v>
       </c>
-      <c r="I47" s="6" t="inlineStr"/>
-      <c r="J47" s="3" t="n">
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="2" t="n">
         <v>95958</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="K47" s="2" t="n">
         <v>353</v>
       </c>
     </row>
